--- a/task4_coref_resolution/output/evaluation_report.xlsx
+++ b/task4_coref_resolution/output/evaluation_report.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -491,7 +491,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,54 +534,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>demonstrative_location</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>demonstrative_location</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>demonstrative_phrase</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -596,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,14 +606,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -646,14 +628,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -664,30 +646,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -704,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,12 +706,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>故宫_故宫_travelog_4_12</t>
+          <t>泰山_泰山_travelog_1_7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>在这里,悬崖为游乐场特了一层实景体验的滤镜</t>
+          <t>下午14:45 我们抵达岱庙,这里是历代帝王封禅泰山的行宫,有千年的古柏、宋代的天贶殿、海量的碑刻,...</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -757,12 +721,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>奥陶纪</t>
+          <t>岱庙</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>山野</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -774,108 +738,96 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>黄山_黄山_travelog_1_9</t>
+          <t>西湖_西湖_travelog_1_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>根据规划,公园内需建别墅群30000平方米,四星级酒店一处...</t>
+          <t>西湖十景之一,雷峰塔,这里可以俯瞰整个西湖全景,景色非常壮观,门票40元,建议坐电梯上去,不然爬楼梯...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>园内</t>
+          <t>这里</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>公园</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>半山</t>
-        </is>
-      </c>
+          <t>雷峰塔</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>incorrect_resolution</t>
+          <t>not_resolved</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>九寨沟_九寨沟_travelog_1_3</t>
+          <t>张家界_张家界_travelog_1_3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>郫县因"杜宇化鹃"的美丽传说郫县又称鹃城县花为杜鹃花县鸟为杜鹃鸟.历史文化遗迹众多望丛祠,杜鹃城遗址...</t>
+          <t>第一站我们去了黄石寨,这里是张家界国家森林公园最大的凌空观景台,有'不上黄石寨,枉到张家界'的说法.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>他们</t>
+          <t>这里</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>望帝和丛帝</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>杜鹃</t>
-        </is>
-      </c>
+          <t>黄石寨</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>incorrect_resolution</t>
+          <t>not_resolved</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>九寨沟_九寨沟_travelog_3_7</t>
+          <t>泰山_泰山_travelog_2_3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>他历经艰险困厄,幡然醒悟,于是苦行修炼,还勇斗孽龙,降魔治水,终成正果,得赐金身天龙.能施降甘霖,惠...</t>
+          <t>我们遇到了很多挑山工，他们真的很辛苦，一步步背着重物上山。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>他</t>
+          <t>他们</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>十三太子</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>龙王</t>
-        </is>
-      </c>
+          <t>挑山工</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>incorrect_resolution</t>
+          <t>not_resolved</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>九寨沟_九寨沟_travelog_4_11</t>
+          <t>泰山_泰山_travelog_2_5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2020年2019年3月27日,我们与四川签署协同提高旅游业发展合同,它是两省区拓张经贸,搭建发展双...</t>
+          <t>关于登山杖，建议在山下买，它能帮你省很多力气。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -885,49 +837,645 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>合同</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>旅游业</t>
-        </is>
-      </c>
+          <t>登山杖</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>incorrect_resolution</t>
+          <t>not_resolved</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>九寨沟_九寨沟_travelog_3_3</t>
+          <t>西湖_西湖_travelog_2_4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>这里,山谷林木蓊郁,枫叶红过又随山风飘落,那枝头的红叶摇成小旗,在欢呼,歌唱,幽静的文昌阁则矗守在半...</t>
+          <t>在断桥可以看到远处的宝石山，它在夕阳下显得格外美丽。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>它</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>宝石山</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张家界_张家界_travelog_2_2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>百龙天梯非常快，它可以在几分钟内把游客送上山顶。</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>它</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>百龙天梯</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张家界_张家界_travelog_2_6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>金鞭溪的水很清澈，这里有很多猴子，千万不要手里拿着食物。</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>这里</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>九寨沟</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>龙潭</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>金鞭溪</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>西湖_西湖_travelog_3_1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>苏堤春晓是西湖十景之首，这个景点全长近3公里，两旁种满了柳树。</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>这个景点</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>苏堤</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>泰山_泰山_travelog_3_2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>十八盘是泰山最险的一段路，这里垂直高度有400多米。</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>这里</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>十八盘</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>泰山_泰山_travelog_3_4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>南天门就在眼前，它是天庭的入口，气势磅礴。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>它</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>南天门</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>西湖_西湖_travelog_4_1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>三潭印月在湖中心，需要坐船过去，那里是人民币一元背后的图案。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>那里</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>三潭印月</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>张家界_张家界_travelog_3_5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>天子山的御笔峰很特别，它像倒插的毛笔，非常逼真。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>它</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>御笔峰</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>张家界_张家界_travelog_4_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>导游非常热情，他给我们讲解了很多关于阿凡达取景地的故事。</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>他</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>导游</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>西湖_西湖_travelog_5_3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>我们在楼外楼吃了午饭，这里的西湖醋鱼味道一般，但东坡肉不错。</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>这里</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>楼外楼</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>西湖</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>incorrect_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>泰山_泰山_travelog_4_1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>红门是徒步的起点，这里有很多卖香火的店铺。</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>这里</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>红门</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>西湖_西湖_travelog_5_5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>灵隐寺香火很旺，这里求签很灵，很多人来还愿。</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>这里</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>灵隐寺</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>西湖</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>incorrect_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>张家界_张家界_travelog_5_1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>十里画廊不需要爬山，可以选择坐小火车，它会带着你穿过峡谷。</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>它</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>小火车</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>金鞭溪</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>incorrect_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>泰山_泰山_travelog_5_2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>玉皇顶是泰山的最高点，这里可以看到云海和日出。</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>这里</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>玉皇顶</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>天外村</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>incorrect_resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>西湖_西湖_travelog_3_4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>花港观鱼有很多红鲤鱼，它们在水里抢食，非常有趣。</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>它们</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>红鲤鱼</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>张家界_张家界_travelog_1_5</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>袁家界是核心景区，该景区拥有天下第一桥和哈利路亚山。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>该景区</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>袁家界</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>泰山_泰山_travelog_2_1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>泰安高铁站离景区有点远，建议打车，或者坐直通大巴，它能直接送到天外村。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>它</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>直通大巴</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>西湖_西湖_travelog_4_3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>曲院风荷在夏天最美，这里有大片的荷花，拍照很出片。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>这里</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>曲院风荷</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>张家界_张家界_travelog_4_4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>杨家界的天然长城很壮观，它是由峰墙组成的奇观。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>它</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>天然长城</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>泰山_泰山_travelog_1_2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>碧霞祠供奉着泰山老奶奶，这里是道教名山的核心。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>这里</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>碧霞祠</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>西湖_西湖_travelog_2_1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>我们在湖滨银泰吃了饭，这里有很多网红餐厅。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>这里</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>湖滨银泰</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>张家界_张家界_travelog_5_3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>山上的猴子很凶，它们会抢游客的包，要注意安全。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>它们</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>猴子</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>not_resolved</t>
         </is>
       </c>
     </row>
